--- a/StructureDefinition-ncpi-drs-file.xlsx
+++ b/StructureDefinition-ncpi-drs-file.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -376,7 +376,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -740,7 +740,7 @@
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.class</t>
@@ -758,7 +758,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|Group|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -824,7 +824,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -858,7 +858,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -892,7 +892,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1014,7 +1014,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1076,7 +1076,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1392,7 +1392,7 @@
     <t>Document Format Codes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/formatcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.meta.profile</t>
@@ -1489,7 +1489,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1579,7 +1579,7 @@
     <t>XDS Facility Type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.0.1</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -1612,7 +1612,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -1621,7 +1621,7 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1637,7 +1637,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1974,7 +1974,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.62890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-drs-file.xlsx
+++ b/StructureDefinition-ncpi-drs-file.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-ncpi-drs-file.xlsx
+++ b/StructureDefinition-ncpi-drs-file.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-drs-file.xlsx
+++ b/StructureDefinition-ncpi-drs-file.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-drs-file.xlsx
+++ b/StructureDefinition-ncpi-drs-file.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
